--- a/artfynd/A 38409-2024 artfynd.xlsx
+++ b/artfynd/A 38409-2024 artfynd.xlsx
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120829541</v>
+        <v>120817983</v>
       </c>
       <c r="B5" t="n">
-        <v>79679</v>
+        <v>57348</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,37 +1012,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Villola V, Ång</t>
+          <t>Forsgrensberget, Forsgrensberget, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>619689</v>
+        <v>619682</v>
       </c>
       <c r="R5" t="n">
-        <v>6970580</v>
+        <v>6970738</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1069,19 +1074,9 @@
           <t>2024-11-02</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>13:42</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-11-02</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>13:42</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1096,19 +1091,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Johan Råghall, Maria Danvind, Fatima Boukarchid</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120829540</v>
+        <v>120829541</v>
       </c>
       <c r="B6" t="n">
         <v>79679</v>
@@ -1148,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>619686</v>
+        <v>619689</v>
       </c>
       <c r="R6" t="n">
-        <v>6970567</v>
+        <v>6970580</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1178,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1193,7 +1188,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120817983</v>
+        <v>120829540</v>
       </c>
       <c r="B7" t="n">
-        <v>57348</v>
+        <v>79679</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1236,42 +1231,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Forsgrensberget, Forsgrensberget, Ång</t>
+          <t>Villola V, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>619682</v>
+        <v>619686</v>
       </c>
       <c r="R7" t="n">
-        <v>6970738</v>
+        <v>6970567</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1298,9 +1288,19 @@
           <t>2024-11-02</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-11-02</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1315,12 +1315,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Johan Råghall, Maria Danvind, Fatima Boukarchid</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -3579,10 +3579,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120829546</v>
+        <v>120829522</v>
       </c>
       <c r="B28" t="n">
-        <v>98071</v>
+        <v>78598</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3591,25 +3591,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3619,10 +3619,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>619659</v>
+        <v>619791</v>
       </c>
       <c r="R28" t="n">
-        <v>6970791</v>
+        <v>6970305</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3654,7 +3654,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3664,7 +3664,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3691,10 +3691,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120829522</v>
+        <v>120829546</v>
       </c>
       <c r="B29" t="n">
-        <v>78598</v>
+        <v>98071</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3703,25 +3703,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3731,10 +3731,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>619791</v>
+        <v>619659</v>
       </c>
       <c r="R29" t="n">
-        <v>6970305</v>
+        <v>6970791</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3766,7 +3766,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 38409-2024 artfynd.xlsx
+++ b/artfynd/A 38409-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120819571</v>
+        <v>120829543</v>
       </c>
       <c r="B2" t="n">
-        <v>79216</v>
+        <v>98081</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Abborrtjärnen, Abborrtjärnen, Ång</t>
+          <t>Villola V, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>619815</v>
+        <v>619675</v>
       </c>
       <c r="R2" t="n">
-        <v>6970198</v>
+        <v>6970719</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,9 +748,19 @@
           <t>2024-11-02</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-11-02</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,12 +775,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Johan Råghall, Maria Danvind, Fatima Boukarchid</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -780,7 +790,7 @@
         <v>120816506</v>
       </c>
       <c r="B3" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -884,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120829552</v>
+        <v>120829538</v>
       </c>
       <c r="B4" t="n">
-        <v>98071</v>
+        <v>78601</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,25 +906,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>619731</v>
+        <v>619842</v>
       </c>
       <c r="R4" t="n">
-        <v>6970320</v>
+        <v>6970132</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +979,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +1006,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120817983</v>
+        <v>120829540</v>
       </c>
       <c r="B5" t="n">
-        <v>57348</v>
+        <v>79682</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,42 +1022,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Forsgrensberget, Forsgrensberget, Ång</t>
+          <t>Villola V, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>619682</v>
+        <v>619686</v>
       </c>
       <c r="R5" t="n">
-        <v>6970738</v>
+        <v>6970567</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1074,9 +1079,19 @@
           <t>2024-11-02</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-11-02</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1091,22 +1106,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Johan Råghall, Maria Danvind, Fatima Boukarchid</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120829541</v>
+        <v>120819585</v>
       </c>
       <c r="B6" t="n">
-        <v>79679</v>
+        <v>78338</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,37 +1134,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Villola V, Ång</t>
+          <t>Abborrtjärnen, Abborrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>619689</v>
+        <v>619815</v>
       </c>
       <c r="R6" t="n">
-        <v>6970580</v>
+        <v>6970198</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1176,19 +1191,9 @@
           <t>2024-11-02</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>13:42</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-11-02</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>13:42</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1203,22 +1208,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Johan Råghall, Maria Danvind, Fatima Boukarchid</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120829540</v>
+        <v>120818098</v>
       </c>
       <c r="B7" t="n">
-        <v>79679</v>
+        <v>57351</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1231,37 +1236,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Villola V, Ång</t>
+          <t>Forsgrensberget, Forsgrensberget, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>619686</v>
+        <v>619682</v>
       </c>
       <c r="R7" t="n">
-        <v>6970567</v>
+        <v>6970738</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1288,19 +1298,9 @@
           <t>2024-11-02</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>13:43</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-11-02</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>13:43</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1315,22 +1315,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Johan Råghall, Maria Danvind, Fatima Boukarchid</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120817102</v>
+        <v>120819571</v>
       </c>
       <c r="B8" t="n">
-        <v>57501</v>
+        <v>79219</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1343,34 +1343,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Forsgrensberget, Forsgrensberget, Ång</t>
+          <t>Abborrtjärnen, Abborrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>619702</v>
+        <v>619815</v>
       </c>
       <c r="R8" t="n">
-        <v>6970607</v>
+        <v>6970198</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1429,10 +1429,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120829538</v>
+        <v>120829548</v>
       </c>
       <c r="B9" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1469,10 +1469,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>619842</v>
+        <v>619691</v>
       </c>
       <c r="R9" t="n">
-        <v>6970132</v>
+        <v>6970817</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1541,10 +1541,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120829543</v>
+        <v>120829541</v>
       </c>
       <c r="B10" t="n">
-        <v>98071</v>
+        <v>79682</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1553,25 +1553,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1581,10 +1581,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>619675</v>
+        <v>619689</v>
       </c>
       <c r="R10" t="n">
-        <v>6970719</v>
+        <v>6970580</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1616,7 +1616,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1653,10 +1653,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120829547</v>
+        <v>120816200</v>
       </c>
       <c r="B11" t="n">
-        <v>98071</v>
+        <v>78601</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1665,41 +1665,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Villola V, Ång</t>
+          <t>Abborrtjärnen, Abborrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>619664</v>
+        <v>619762</v>
       </c>
       <c r="R11" t="n">
-        <v>6970824</v>
+        <v>6970348</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1726,19 +1726,9 @@
           <t>2024-11-02</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>13:06</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-11-02</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>13:06</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1753,22 +1743,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Johan Råghall, Maria Danvind, Fatima Boukarchid</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120829550</v>
+        <v>120816642</v>
       </c>
       <c r="B12" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1801,22 +1791,22 @@
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Villola V, Ång</t>
+          <t>Forsgrensberget, Forsgrensberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>619693</v>
+        <v>619719</v>
       </c>
       <c r="R12" t="n">
-        <v>6970706</v>
+        <v>6970497</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1843,24 +1833,9 @@
           <t>2024-11-02</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>12:54</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-11-02</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>12:54</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1875,22 +1850,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Johan Råghall, Maria Danvind, Fatima Boukarchid</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120818271</v>
+        <v>120816689</v>
       </c>
       <c r="B13" t="n">
-        <v>90687</v>
+        <v>78601</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1903,21 +1878,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1927,10 +1902,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>619659</v>
+        <v>619719</v>
       </c>
       <c r="R13" t="n">
-        <v>6970828</v>
+        <v>6970497</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1989,10 +1964,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120829536</v>
+        <v>120817102</v>
       </c>
       <c r="B14" t="n">
-        <v>79679</v>
+        <v>57504</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2005,40 +1980,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Villola V, Ång</t>
+          <t>Forsgrensberget, Forsgrensberget, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>619850</v>
+        <v>619702</v>
       </c>
       <c r="R14" t="n">
-        <v>6970151</v>
+        <v>6970607</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2065,65 +2037,39 @@
           <t>2024-11-02</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>14:12</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-11-02</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>14:12</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Johan Råghall, Maria Danvind, Fatima Boukarchid</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120829535</v>
+        <v>120818271</v>
       </c>
       <c r="B15" t="n">
-        <v>79679</v>
+        <v>90697</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2136,40 +2082,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Villola V, Ång</t>
+          <t>Forsgrensberget, Forsgrensberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>619855</v>
+        <v>619659</v>
       </c>
       <c r="R15" t="n">
-        <v>6970208</v>
+        <v>6970828</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2196,65 +2139,39 @@
           <t>2024-11-02</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>14:16</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-11-02</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>14:16</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Johan Råghall, Maria Danvind, Fatima Boukarchid</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120816200</v>
+        <v>120827272</v>
       </c>
       <c r="B16" t="n">
-        <v>78598</v>
+        <v>57351</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2267,37 +2184,45 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Abborrtjärnen, Abborrtjärnen, Ång</t>
+          <t>Forsgrensberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>619762</v>
+        <v>619724</v>
       </c>
       <c r="R16" t="n">
-        <v>6970348</v>
+        <v>6970494</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2341,22 +2266,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fatima Boukarchid</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fatima Boukarchid</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120829551</v>
+        <v>120816368</v>
       </c>
       <c r="B17" t="n">
-        <v>78598</v>
+        <v>57351</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2369,37 +2294,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Villola V, Ång</t>
+          <t>Abborrtjärnen, Abborrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>619735</v>
+        <v>619762</v>
       </c>
       <c r="R17" t="n">
-        <v>6970338</v>
+        <v>6970348</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2426,19 +2351,9 @@
           <t>2024-11-02</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>11:36</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-11-02</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>11:36</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2453,22 +2368,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Johan Råghall, Maria Danvind, Fatima Boukarchid</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120827272</v>
+        <v>120829547</v>
       </c>
       <c r="B18" t="n">
-        <v>57348</v>
+        <v>98081</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2477,49 +2392,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Forsgrensberget, Ång</t>
+          <t>Villola V, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>619724</v>
+        <v>619664</v>
       </c>
       <c r="R18" t="n">
-        <v>6970494</v>
+        <v>6970824</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2546,9 +2453,19 @@
           <t>2024-11-02</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-11-02</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2563,22 +2480,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Fatima Boukarchid</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Fatima Boukarchid</t>
+          <t>Johan Råghall, Maria Danvind, Fatima Boukarchid</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120817725</v>
+        <v>120818230</v>
       </c>
       <c r="B19" t="n">
-        <v>57348</v>
+        <v>98081</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2587,31 +2504,30 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>200</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2620,10 +2536,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>619720</v>
+        <v>619659</v>
       </c>
       <c r="R19" t="n">
-        <v>6970630</v>
+        <v>6970828</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2656,6 +2572,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-11-02</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Rikligt. Två växtplatser</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2682,10 +2603,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120819533</v>
+        <v>120817301</v>
       </c>
       <c r="B20" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2718,19 +2639,19 @@
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Abborrtjärnen, Abborrtjärnen, Ång</t>
+          <t>Forsgrensberget, Forsgrensberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>619790</v>
+        <v>619720</v>
       </c>
       <c r="R20" t="n">
-        <v>6970271</v>
+        <v>6970630</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2789,10 +2710,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120829549</v>
+        <v>120829522</v>
       </c>
       <c r="B21" t="n">
-        <v>57348</v>
+        <v>78601</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2805,42 +2726,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Villola V, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>619678</v>
+        <v>619791</v>
       </c>
       <c r="R21" t="n">
-        <v>6970741</v>
+        <v>6970305</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2872,7 +2785,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2882,12 +2795,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:58</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2914,10 +2822,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120816642</v>
+        <v>120829550</v>
       </c>
       <c r="B22" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2950,22 +2858,22 @@
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Forsgrensberget, Forsgrensberget, Ång</t>
+          <t>Villola V, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>619719</v>
+        <v>619693</v>
       </c>
       <c r="R22" t="n">
-        <v>6970497</v>
+        <v>6970706</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2992,9 +2900,24 @@
           <t>2024-11-02</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-11-02</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3009,22 +2932,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Johan Råghall, Maria Danvind, Fatima Boukarchid</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120819585</v>
+        <v>120819533</v>
       </c>
       <c r="B23" t="n">
-        <v>78335</v>
+        <v>57351</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3037,34 +2960,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Abborrtjärnen, Abborrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>619815</v>
+        <v>619790</v>
       </c>
       <c r="R23" t="n">
-        <v>6970198</v>
+        <v>6970271</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -3123,10 +3051,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120829537</v>
+        <v>120829536</v>
       </c>
       <c r="B24" t="n">
-        <v>79639</v>
+        <v>79682</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3135,25 +3063,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3201,7 +3129,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3211,7 +3139,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3254,10 +3182,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120829548</v>
+        <v>120829537</v>
       </c>
       <c r="B25" t="n">
-        <v>78598</v>
+        <v>79642</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3266,38 +3194,41 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Villola V, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>619691</v>
+        <v>619850</v>
       </c>
       <c r="R25" t="n">
-        <v>6970817</v>
+        <v>6970151</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3329,7 +3260,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3339,7 +3270,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3348,8 +3279,24 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3366,10 +3313,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120818230</v>
+        <v>120829539</v>
       </c>
       <c r="B26" t="n">
-        <v>98071</v>
+        <v>78601</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3378,45 +3325,41 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Forsgrensberget, Forsgrensberget, Ång</t>
+          <t>Villola V, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>619659</v>
+        <v>619815</v>
       </c>
       <c r="R26" t="n">
-        <v>6970828</v>
+        <v>6970166</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3443,14 +3386,19 @@
           <t>2024-11-02</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-11-02</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Rikligt. Två växtplatser</t>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3465,22 +3413,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Johan Råghall, Maria Danvind, Fatima Boukarchid</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120816689</v>
+        <v>120829551</v>
       </c>
       <c r="B27" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3513,17 +3461,17 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Forsgrensberget, Forsgrensberget, Ång</t>
+          <t>Villola V, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>619719</v>
+        <v>619735</v>
       </c>
       <c r="R27" t="n">
-        <v>6970497</v>
+        <v>6970338</v>
       </c>
       <c r="S27" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3550,9 +3498,19 @@
           <t>2024-11-02</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-11-02</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3567,22 +3525,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Johan Råghall, Maria Danvind, Fatima Boukarchid</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120829522</v>
+        <v>120829546</v>
       </c>
       <c r="B28" t="n">
-        <v>78598</v>
+        <v>98081</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3591,25 +3549,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3619,10 +3577,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>619791</v>
+        <v>619659</v>
       </c>
       <c r="R28" t="n">
-        <v>6970305</v>
+        <v>6970791</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3654,7 +3612,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3664,7 +3622,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3691,10 +3649,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120829546</v>
+        <v>120829552</v>
       </c>
       <c r="B29" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3731,10 +3689,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>619659</v>
+        <v>619731</v>
       </c>
       <c r="R29" t="n">
-        <v>6970791</v>
+        <v>6970320</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3766,7 +3724,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3776,7 +3734,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3803,10 +3761,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120829539</v>
+        <v>120829535</v>
       </c>
       <c r="B30" t="n">
-        <v>78598</v>
+        <v>79682</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3819,34 +3777,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Villola V, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>619815</v>
+        <v>619855</v>
       </c>
       <c r="R30" t="n">
-        <v>6970166</v>
+        <v>6970208</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3878,7 +3839,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3888,7 +3849,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3897,8 +3858,24 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -3915,10 +3892,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120816368</v>
+        <v>120829549</v>
       </c>
       <c r="B31" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3949,19 +3926,27 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Abborrtjärnen, Abborrtjärnen, Ång</t>
+          <t>Villola V, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>619762</v>
+        <v>619678</v>
       </c>
       <c r="R31" t="n">
-        <v>6970348</v>
+        <v>6970741</v>
       </c>
       <c r="S31" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3988,9 +3973,24 @@
           <t>2024-11-02</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-11-02</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4005,12 +4005,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Johan Råghall, Maria Danvind, Fatima Boukarchid</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>

--- a/artfynd/A 38409-2024 artfynd.xlsx
+++ b/artfynd/A 38409-2024 artfynd.xlsx
@@ -2492,10 +2492,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120818230</v>
+        <v>120817301</v>
       </c>
       <c r="B19" t="n">
-        <v>98081</v>
+        <v>57351</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2504,30 +2504,31 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>200</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2536,10 +2537,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>619659</v>
+        <v>619720</v>
       </c>
       <c r="R19" t="n">
-        <v>6970828</v>
+        <v>6970630</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2572,11 +2573,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-11-02</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Rikligt. Två växtplatser</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2603,10 +2599,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120817301</v>
+        <v>120829522</v>
       </c>
       <c r="B20" t="n">
-        <v>57351</v>
+        <v>78601</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2619,42 +2615,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Forsgrensberget, Forsgrensberget, Ång</t>
+          <t>Villola V, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>619720</v>
+        <v>619791</v>
       </c>
       <c r="R20" t="n">
-        <v>6970630</v>
+        <v>6970305</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2681,9 +2672,19 @@
           <t>2024-11-02</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-11-02</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2698,22 +2699,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Johan Råghall, Maria Danvind, Fatima Boukarchid</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120829522</v>
+        <v>120818230</v>
       </c>
       <c r="B21" t="n">
-        <v>78601</v>
+        <v>98081</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2722,41 +2723,45 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Villola V, Ång</t>
+          <t>Forsgrensberget, Forsgrensberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>619791</v>
+        <v>619659</v>
       </c>
       <c r="R21" t="n">
-        <v>6970305</v>
+        <v>6970828</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2783,19 +2788,14 @@
           <t>2024-11-02</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>15:29</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-11-02</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>15:29</t>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Rikligt. Två växtplatser</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2810,12 +2810,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Johan Råghall, Maria Danvind, Fatima Boukarchid</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>

--- a/artfynd/A 38409-2024 artfynd.xlsx
+++ b/artfynd/A 38409-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY41"/>
+  <dimension ref="A1:AZ41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120818271</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120819051</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120827018</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1082,6 +1102,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120829545</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1179,6 +1204,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120819043</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1286,6 +1316,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120829544</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1383,6 +1418,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120818622</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1480,6 +1520,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120816200</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1577,6 +1622,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120816689</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1674,6 +1724,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120819994</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1781,6 +1836,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120829522</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1888,6 +1948,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120829538</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1995,6 +2060,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120829539</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2102,6 +2172,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120829548</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2209,6 +2284,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120829551</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2306,6 +2386,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120819571</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2403,6 +2488,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120818321</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2529,6 +2619,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120829535</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2655,6 +2750,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120829536</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2762,6 +2862,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120829540</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2869,6 +2974,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120829541</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2999,6 +3109,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120829542</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3096,6 +3211,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120816368</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3198,6 +3318,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120816506</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3300,6 +3425,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120816642</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3402,6 +3532,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120817301</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3504,6 +3639,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120817983</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3606,6 +3746,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120819533</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3716,6 +3861,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120827264</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3836,6 +3986,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120829549</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3953,6 +4108,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120829550</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4050,6 +4210,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120817102</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4156,6 +4321,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120818230</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4263,6 +4433,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120829543</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4370,6 +4545,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120829546</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4477,6 +4657,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120829547</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4584,6 +4769,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120829552</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4685,6 +4875,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128077567</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4782,6 +4977,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120819585</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4908,8 +5108,55 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120829537</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>